--- a/config/yunying/dispatch.xlsx
+++ b/config/yunying/dispatch.xlsx
@@ -1605,7 +1605,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>新しい探検</t>
+          <t>新的探索</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>小智と仲間たちは新しいエリアを発見した。そこ美しい景色が広がっています。彼らは周囲の探索を始めた。</t>
+          <t>小智和伙伴们发现了新的区域。那里美丽的景色蔓延开来。他们开始在周围搜索。</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1707,14 +1707,14 @@
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
+          <t>大扫除</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>大掃除</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>大掃除</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>Thorough cleaning</t>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="I5" s="1" t="inlineStr">
         <is>
-          <t>一軒の家があり、中に入ると、部屋の中は埃が舞い、散らかっていた。しかし、仲間たちの助けがあれば、すぐに片付けられるだろう。</t>
+          <t>有一户人家，进去一看，屋里尘土飞扬，乱七八糟。但如果有队友们的帮助，应该很快就能收拾好。</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>愛の原動力</t>
+          <t>爱的动力</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>ここの研究所の電気回路が故障し、機械が正常に動作していない。{0}は信頼できる仲間を派遣して助けよう！</t>
+          <t>这家研究所的电路发生故障，机器不能正常工作。{0}派遣可靠的伙伴来帮助吧！</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>神秘な香り</t>
+          <t>神秘的香味</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>小智一行は旅を続けようとしたが、突然、果実の香りが風に乗って漂ってきた。その香りに惹かれ、一行は調査に向かうことを決めました。</t>
+          <t>小智一行正准备继续旅行，突然一阵果香随风飘来。被那个香味吸引，一行人决定去调查。</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>継続進行Ⅰ</t>
+          <t>继续进行Ⅰ</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>小智と仲間たちは道を進みながら、小智の指示に従いチームに分かれました。探索中の安全を確保するための布陣です。</t>
+          <t>小智和伙伴们一边前进，一边按照小智的指示分组。这是为了确保搜索过程中的安全的布阵。</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>継続進行Ⅱ</t>
+          <t>继续进行Ⅱ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>小智と仲間たちは道を進みながら、小智の指示に従いチームに分かれました。探索中の安全を確保するための布陣です。</t>
+          <t>小智和伙伴们一边前进，一边按照小智的指示分组。这是为了确保搜索过程中的安全的布阵。</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ピクニック</t>
+          <t>野餐</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>この小さな林はあまり広くないけど、木になっている野生の果実はとてもみずみずしくて美味しそうだ。小智と仲間たちはここで少し休むことにした。</t>
+          <t>这片小树林虽然不大，但树上的野果看起来很新鲜很好吃。小智和伙伴们决定在这里稍事休息。</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>忘れられた遺跡</t>
+          <t>被遗忘的遗迹</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>目の前には模様が刻まれた石柱が道を塞いでいる。小智は慎重に石柱をどけることにした。もしかしたら、何かの遺跡の古代の品かもしれない</t>
+          <t>眼前刻有花纹的石柱挡住了道路。小智决定小心翼翼地移开石柱。说不定是某个遗迹的古代文物</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>継続進行Ⅲ</t>
+          <t>继续进行Ⅲ</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>小智と仲間たちは道を進みながら、小智の指示に従いチームに分かれました。探索中の安全を確保するための布陣です。</t>
+          <t>小智和伙伴们一边前进，一边按照小智的指示分组。这是为了确保搜索过程中的安全的布阵。</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>川を渡るⅠ</t>
+          <t>过河Ⅰ</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>小智一行は川辺にたどり着いたが、川にかかる木の橋は渡るには危険そうだった。そこで小智は仲間たちに川を歩いて渡るよう指示することにした。</t>
+          <t>小智一行人好不容易来到河边，但河上的木桥似乎很危险。于是小智指示伙伴们步行过河。</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>川を渡るⅡ</t>
+          <t>过河Ⅱ</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>川を一つ渡り終えたものの、さらに幅の広い川が目の前に現れた。小智と仲間たちは仕方なく再び川を渡ることになった。</t>
+          <t>虽然过了一条河，但眼前又出现了一条更宽的河。小智和伙伴们只好再次渡河。</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>空飛ぶ人</t>
+          <t>空中飞人</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>小智一行はようやく川を離れ、広がる青々とした山の麓にたどり着いた。山は雲に届くほど高くそびえ立ち、小智は自分を“飛ぶ”方法で登ることを考えた。</t>
+          <t>小智一行终于离开河川，来到一片青翠的山麓。山高耸入云，小智想用“飞”的方式让自己爬上去。</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>焚き火</t>
+          <t>篝火</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>木陰に覆われた山々の中は本当に少し寒い。小智は焚き火をしようと考え、仲間たちの助けが必要だった。</t>
+          <t>树荫覆盖的山里真有点冷。小智想生火，需要伙伴们的帮助。</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>探検準備</t>
+          <t>探险准备</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="I17" s="1" t="inlineStr">
         <is>
-          <t>山を越えると、目の前には果てしなく広がる砂漠地帯が現れ、気候が暑くなった。砂漠に入る前、しっかりと準備を整えなければならない。</t>
+          <t>过了山，眼前是一望无际的沙漠地带，天气变得炎热。在进入沙漠之前，必须做好充分的准备。</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>罠を解除</t>
+          <t>解除陷阱</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>小智一行は腰ほどの高さの草むらを抜ける必要があるが、猟師が仕掛けた罠が潜んでいるようだ。とても危険なため、まずは罠を片付ける必要がある。</t>
+          <t>小智一行必须穿过齐腰高的草丛，但似乎隐藏着猎人设下的陷阱。因为非常危险，所以首先要清除陷阱。</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>継続進行Ⅳ</t>
+          <t>继续进行Ⅳ</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>小智と仲間たちは道を進みながら、小智の指示に従いチームに分かれました。探索中の安全を確保するための布陣です。</t>
+          <t>小智和伙伴们一边前进，一边按照小智的指示分组。这是为了确保搜索过程中的安全的布阵。</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>異界</t>
+          <t>异界</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>道端の草が何かに踏み潰されたように倒れていて、遠くまで続いている。なんとも奇妙な光景に、小智は仲間たちと一緒に近づいて調べる事にした。</t>
+          <t>路边的小草像是被什么东西踩扁了似的倒在地上，一直延伸到远处。面对如此奇妙的光景，小智决定和伙伴们一起靠近调查。</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>継続進行Ⅴ</t>
+          <t>继续进行Ⅴ</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>小智と仲間たちは道を進みながら、小智の指示に従いチームに分かれました。探索中の安全を確保するための布陣です。</t>
+          <t>小智和伙伴们一边前进，一边按照小智的指示分组。这是为了确保搜索过程中的安全的布阵。</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>生命の源</t>
+          <t>生命之源</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>小智一行はひたすら道を急ぎ、喉の渇きが限界に達していた。ようやく道端に茂る緑の植物を見つけ、それを使って命の水を得ることにした。</t>
+          <t>小智一行只顾赶路，口渴到了极限。终于在路边发现了茂密的绿色植物，决定用它来获取生命之水。</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>砂漠に入ると早速分かれ道があった。小道は狭く細いが、遠くには美しい景色が見えそうだ。小智は探検用の部隊を派遣して調査することにした。</t>
+          <t>一进入沙漠就有岔路。小路狭窄，但远处似乎能看到美丽的景色。小智决定派遣一支探险部队前去调查。</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="I24" s="1" t="inlineStr">
         <is>
-          <t>強い日差しが大地を照らし、ついには道端の枯れ木が燃え上がった。濃い黒煙と熱気が行く手を阻み、すぐに火を消さなければならない。</t>
+          <t>强烈的阳光照耀大地，路边的枯树终于燃烧起来。浓浓的黑烟和热气阻挡了去路，必须马上灭火。</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="I25" s="1" t="inlineStr">
         <is>
-          <t>道のそばに小さな丘があり、砂漠の気候がその形に風化させている。この場所には新しい仲間が住んでいるのだろうか？</t>
+          <t>路边有个小山丘，沙漠气候风化了它的形状。这个地方住着新的伙伴吗？</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>ここは小町へ向かう最速の道のはずだが、前方で道が途切れてしまっている。小智は地形を把握するため、仲間たちと手分けして調査することにした。</t>
+          <t>这里应该是前往小町最快的路，但前方的路已经断了。小智为了掌握地形，决定和伙伴们分头调查。</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
-          <t>博愛主義</t>
+          <t>博爱主义</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>前方に小町へ続く道が見えるようだ。その道の脇では誰かが植栽をしているように見える。小智は手伝うことに決めた。</t>
+          <t>前方似乎可以看到通往小町的道路。那条路的旁边好像有人在种植植物。小智决定帮忙。</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>これで砂漠で分かれ道に出くわすのは2回目だ。前回の経験から、小智と仲間たちはここで“宝物”を見逃したくないと思っている。</t>
+          <t>这是我第二次在沙漠中遇到岔路口。由于上次的经验，小智和小伙伴们不想在这里错过“宝物”。</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>道を聞くⅠ</t>
+          <t>问路Ⅰ</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>道端から少し離れたところに一軒の低い家があり、誰かが住んでいるようだ。小智は仲間を数人連れて道を尋ねに行くことにした。</t>
+          <t>离路边不远的地方有一间低矮的房子，好像有人住在里面。小智决定带几个伙伴去问路。</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>道を聞くⅡ</t>
+          <t>问路Ⅱ</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>住民の指示に従って、小智一行はすぐに近くの小町を見つけた。すでに夜が更けているため、小智は急いで宿泊場所を探すことにした。</t>
+          <t>根据居民的指示，小智一行很快就找到了附近的小町。夜已深，小智决定赶紧找住宿的地方。</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="I31" s="1" t="inlineStr">
         <is>
-          <t>また分かれ道！ただ、今回の分かれ道は遠くまで続いているようだ。この道を進むには、十分に注意が必要だ。</t>
+          <t>又是岔路口！只是，这次的岔路口似乎一直延伸到很远的地方。走这条路需要非常小心。</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>準備万端</t>
+          <t>准备就绪</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="I32" s="1" t="inlineStr">
         <is>
-          <t>暑い天候の中、何度も進み続けたことで仲間たちが疲れている。手作りの氷菓を用意すれば、暑さを和らげることができるかもしれない。</t>
+          <t>在炎热的天气中多次前进，伙伴们都累了。如果准备一些手工制作的冰棍，或许可以缓解酷暑。</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>夏の砂浜</t>
+          <t>夏日沙滩</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>道の果てには果てしなく広がる大海があり、その景色はまさに別世界のようだ。小智一行はここでしばし足を止め、休暇を楽しむことにした！</t>
+          <t>路的尽头是一望无际的大海，那景色仿佛是另一个世界。小智一行决定在此停下脚步，享受假期！</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>小智と仲間たちは、生い茂る緑が美しい森を偶然発見した。守護者の直感が、この場所には新たな仲間がいるかもしれないと告げている。</t>
+          <t>小智和伙伴们偶然发现了一片郁郁葱葱的森林。守护者的直觉告诉他，这个地方可能会有新的伙伴。</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>春の収穫</t>
+          <t>春季收获</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>小道の先には一面に広がる青々とした畑があり、たくさんの果実が実っている。道端には農具も置かれていたため、小智は果実を収穫することにした。</t>
+          <t>小路前方是一片碧绿的田地，结满了果实。路边还放着农具，小智决定采摘果实。</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>やはり、ここは長い間放置されていた畑のようだ。雑草が生い茂り、果実もたくさん実っていて、小智と仲間たちが十分に腹を満たせるほどだ。</t>
+          <t>果然，这里是长期荒废的田地。杂草丛生，果实累累，足以让小智和伙伴们吃饱肚子。</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>摘む</t>
+          <t>摘</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="I38" s="1" t="inlineStr">
         <is>
-          <t>森の木々の葉は密集している。果実は美味しそうだが、収穫するには手間がかかりそうだ。仲間たちの助けがあれば、すぐに食べれるだろう。</t>
+          <t>森林里的树叶很密。果实看起来很好吃，但收获起来很费事。有伙伴们的帮助，马上就可以吃了吧。</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t>悠悠自適</t>
+          <t>悠然自适</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>果実を収穫するのにはかなり手間がかかったが、甘くてジューシーな味わいは格別だった。小智と仲間たちは、あまりの美味しさに手が止まらない。</t>
+          <t>采摘果实颇费功夫，但甘甜多汁的味道别具一格。小智和他的伙伴们，因为太美味而停不下来。</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>川底の財宝</t>
+          <t>河底的宝藏</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="I40" s="1" t="inlineStr">
         <is>
-          <t>仲間たちが上流の川底で大量の“宝物”を発見した！しかし、川の流れは急で危険だ。ここでは水に強い仲間の助けが必要だ！</t>
+          <t>伙伴们在上游的河底发现了大量的“宝物”！但是河流湍急危险。在这里，我们需要一个擅长水性的伙伴的帮助！</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>麓の洞窟</t>
+          <t>山脚下的洞穴</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="I41" s="1" t="inlineStr">
         <is>
-          <t>仲間が山の麓で隠れた洞窟の入口を見つけた。入口は小さいが、かすかに光が漏れている。もしかして、まだ宝物があるのだろうか？</t>
+          <t>伙伴在山脚下发现了一个隐蔽的洞穴入口。入口虽小，但透出微微的光亮。难道还有宝藏吗？</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>空中の財宝</t>
+          <t>空中宝藏</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>飛行属性の仲間が小智に、上空から見るとまるで地図のようなルートが描かれていると教えてくれた。従って進むと、大きな宝箱を発見した！</t>
+          <t>飞行属性的伙伴告诉小智，从上空看，路线就像地图一样。因此，继续前进，发现了一个大宝箱！</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>小さな洞窟</t>
+          <t>小洞穴</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="I43" s="1" t="inlineStr">
         <is>
-          <t>小隊は、道の先に大きな鉱山の洞窟を発見した。洞窟の入り口は広く、門の前には大型フォークリフトが積まれている。作業を進めるには難しそうだ。</t>
+          <t>小队在道路前方发现了一个巨大的矿山洞穴。洞窟入口宽阔，门前堆积着大型叉车。要进行工作好像很难。</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>意外な収穫</t>
+          <t>意外的收获</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="I44" s="1" t="inlineStr">
         <is>
-          <t>この道は現在修理中で、町には行けなかった。幸いにも仲間たちは宝箱を見つけ、中にはたくさんの宝が入っていた！</t>
+          <t>这条路现在正在修理，不能进城。幸运的是，伙伴们发现了一个宝箱，里面有很多宝藏！</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>大きな洞窟</t>
+          <t>大洞穴</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -6561,7 +6561,7 @@
       </c>
       <c r="I45" s="1" t="inlineStr">
         <is>
-          <t>やはり、小隊はまた別の鉱山の洞窟を発見した。今回は前回よりずっと大きく見える。仲間たちはすでに準備万端だ。</t>
+          <t>果然，小队又发现了另一个矿山洞穴。这次看起来比上次大得多。伙伴们已经做好了一切准备。</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>進む</t>
+          <t>走</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="I46" s="1" t="inlineStr">
         <is>
-          <t>半日以上進んだが、どうやら新しい進展はないようだ。奇妙な洞窟も見つからず、小隊はさらに前進して調査を続けることに決めた。</t>
+          <t>进行了半天多，似乎没有新的进展。也没有发现奇怪的洞穴，小队决定继续前进并继续调查。</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t>再度進む</t>
+          <t>再次前进</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="I47" s="1" t="inlineStr">
         <is>
-          <t>分かれ道では鉱山の洞窟どころか、地面の穴すら見当たらない。分隊の仲間には疲れている者もいるが、残りの仲間たちは前進することを決めた。</t>
+          <t>岔路口别说矿山的洞穴了，就连地面上的洞都找不到。分队里有些人已经筋疲力尽了，其余的人决定继续前进。</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
